--- a/config/random_tower/board.xlsx
+++ b/config/random_tower/board.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>豪華宝箱</t>
+          <t>豪华宝箱</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>試練を乗り越えた者に与えられる報酬。</t>
+          <t>给予通过试炼者的报酬。</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>豪華宝箱</t>
+          <t>豪华宝箱</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>試練を乗り越えた者に与えられる報酬。</t>
+          <t>给予通过试炼者的报酬。</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13622,7 +13622,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>豪華宝箱</t>
+          <t>豪华宝箱</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>試練を乗り越えた者に与えられる報酬。</t>
+          <t>给予通过试炼者的报酬。</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -17809,7 +17809,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -18092,7 +18092,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -18154,7 +18154,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -18475,7 +18475,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -18892,7 +18892,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -19108,7 +19108,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -19531,7 +19531,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -20015,7 +20015,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -20753,7 +20753,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -21069,7 +21069,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -21325,7 +21325,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -21417,7 +21417,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -21452,7 +21452,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -21728,7 +21728,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -21877,7 +21877,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -22125,7 +22125,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -22217,7 +22217,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>豪華宝箱</t>
+          <t>豪华宝箱</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -22498,7 +22498,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>試練を乗り越えた者に与えられる報酬。</t>
+          <t>给予通过试炼者的报酬。</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -22654,7 +22654,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -22778,7 +22778,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
@@ -22932,7 +22932,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
@@ -23059,7 +23059,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -23151,7 +23151,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -23243,7 +23243,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -23335,7 +23335,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
@@ -23392,7 +23392,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -23454,7 +23454,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -23578,7 +23578,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
@@ -23926,7 +23926,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -23961,7 +23961,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -24058,7 +24058,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -24155,7 +24155,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -24279,7 +24279,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -24495,7 +24495,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
@@ -24746,7 +24746,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -24781,7 +24781,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -24945,7 +24945,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -24980,7 +24980,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
@@ -25047,7 +25047,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
@@ -25591,7 +25591,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
@@ -25723,7 +25723,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P304" t="inlineStr">
@@ -25785,7 +25785,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -25820,7 +25820,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -25944,7 +25944,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -26068,7 +26068,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -26135,7 +26135,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -26165,7 +26165,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
@@ -26227,7 +26227,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
@@ -26344,7 +26344,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
@@ -26416,7 +26416,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
@@ -26548,7 +26548,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
@@ -26707,7 +26707,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -26742,7 +26742,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P316" t="inlineStr">
@@ -26799,7 +26799,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
@@ -26926,7 +26926,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P319" t="inlineStr">
@@ -27075,7 +27075,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -27110,7 +27110,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
@@ -27167,7 +27167,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -27202,7 +27202,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -27321,7 +27321,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -27383,7 +27383,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -27507,7 +27507,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -27569,7 +27569,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
@@ -27656,7 +27656,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
@@ -27758,7 +27758,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -27793,7 +27793,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>豪華宝箱</t>
+          <t>豪华宝箱</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>試練を乗り越えた者に与えられる報酬。</t>
+          <t>给予通过试炼者的报酬。</t>
         </is>
       </c>
       <c r="P330" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -28009,7 +28009,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P332" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P333" t="inlineStr">
@@ -28168,7 +28168,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -28416,7 +28416,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -28451,7 +28451,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
@@ -28508,7 +28508,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -28543,7 +28543,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
@@ -28635,7 +28635,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -28819,7 +28819,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P342" t="inlineStr">
@@ -28876,7 +28876,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P343" t="inlineStr">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -29030,7 +29030,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -29216,7 +29216,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -29313,7 +29313,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P349" t="inlineStr">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -29405,7 +29405,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -29564,7 +29564,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P353" t="inlineStr">
@@ -29758,7 +29758,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -29793,7 +29793,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P354" t="inlineStr">
@@ -29855,7 +29855,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -29917,7 +29917,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -29979,7 +29979,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -30046,7 +30046,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -30108,7 +30108,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P359" t="inlineStr">
@@ -30200,7 +30200,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -30230,7 +30230,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P360" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P361" t="inlineStr">
@@ -30389,7 +30389,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -30424,7 +30424,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
@@ -30526,7 +30526,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P363" t="inlineStr">
@@ -30588,7 +30588,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P364" t="inlineStr">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -30757,7 +30757,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -30881,7 +30881,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -30978,7 +30978,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P369" t="inlineStr">
@@ -31040,7 +31040,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
@@ -31157,7 +31157,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -31264,7 +31264,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
@@ -31361,7 +31361,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P373" t="inlineStr">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -31458,7 +31458,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P374" t="inlineStr">
@@ -31520,7 +31520,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -31582,7 +31582,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -31644,7 +31644,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -31706,7 +31706,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -31773,7 +31773,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -31803,7 +31803,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P379" t="inlineStr">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -31895,7 +31895,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P380" t="inlineStr">
@@ -31982,7 +31982,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P381" t="inlineStr">
@@ -32054,7 +32054,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P382" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P383" t="inlineStr">
@@ -32248,7 +32248,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -32283,7 +32283,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P384" t="inlineStr">
@@ -32345,7 +32345,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -32380,7 +32380,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
@@ -32437,7 +32437,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P386" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
@@ -32656,7 +32656,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
@@ -32713,7 +32713,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -32748,7 +32748,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P389" t="inlineStr">
@@ -32805,7 +32805,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P390" t="inlineStr">
@@ -32897,7 +32897,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -32959,7 +32959,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -33021,7 +33021,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -33145,7 +33145,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -33207,7 +33207,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -33269,7 +33269,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>何か良いことがあるかもしれない。</t>
+          <t>也许会有什么好事。</t>
         </is>
       </c>
       <c r="P397" t="inlineStr">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -33391,7 +33391,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P398" t="inlineStr">
@@ -33458,7 +33458,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -33493,7 +33493,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P399" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>豪華宝箱</t>
+          <t>豪华宝箱</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -33580,7 +33580,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>試練を乗り越えた者に与えられる報酬。</t>
+          <t>给予通过试炼者的报酬。</t>
         </is>
       </c>
       <c r="P400" t="inlineStr">
@@ -33674,7 +33674,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -33709,7 +33709,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P402" t="inlineStr">
@@ -33811,7 +33811,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P403" t="inlineStr">
@@ -33878,7 +33878,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -34002,7 +34002,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -34037,7 +34037,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P406" t="inlineStr">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -34129,7 +34129,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P407" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P408" t="inlineStr">
@@ -34313,7 +34313,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P409" t="inlineStr">
@@ -34370,7 +34370,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -34405,7 +34405,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P410" t="inlineStr">
@@ -34462,7 +34462,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P411" t="inlineStr">
@@ -34554,7 +34554,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -34616,7 +34616,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -34678,7 +34678,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -34745,7 +34745,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -34812,7 +34812,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -34842,7 +34842,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P416" t="inlineStr">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -34934,7 +34934,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P417" t="inlineStr">
@@ -35021,7 +35021,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P418" t="inlineStr">
@@ -35093,7 +35093,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -35128,7 +35128,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P419" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P420" t="inlineStr">
@@ -35287,7 +35287,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P421" t="inlineStr">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -35446,7 +35446,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -35570,7 +35570,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -35662,7 +35662,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P426" t="inlineStr">
@@ -35724,7 +35724,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P427" t="inlineStr">
@@ -35841,7 +35841,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P428" t="inlineStr">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -35948,7 +35948,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P429" t="inlineStr">
@@ -36050,7 +36050,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P430" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -36147,7 +36147,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P431" t="inlineStr">
@@ -36214,7 +36214,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -36281,7 +36281,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -36343,7 +36343,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -36477,7 +36477,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -36507,7 +36507,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P436" t="inlineStr">
@@ -36569,7 +36569,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P437" t="inlineStr">
@@ -36686,7 +36686,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P438" t="inlineStr">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -36793,7 +36793,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
@@ -36890,7 +36890,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P440" t="inlineStr">
@@ -36952,7 +36952,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -36987,7 +36987,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P441" t="inlineStr">
@@ -37049,7 +37049,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -37111,7 +37111,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -37173,7 +37173,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -37235,7 +37235,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -37297,7 +37297,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -37364,7 +37364,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -37394,7 +37394,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>何が起きるか分からない！</t>
+          <t>我不知道会发生什么！</t>
         </is>
       </c>
       <c r="P447" t="inlineStr">
@@ -37456,7 +37456,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -37486,7 +37486,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>幸運を招くか、災いを呼ぶか誰にも分からない。</t>
+          <t>谁也不知道会带来幸运还是灾难。</t>
         </is>
       </c>
       <c r="P448" t="inlineStr">
@@ -37573,7 +37573,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>偶然見つけた宝箱</t>
+          <t>偶然发现的宝箱</t>
         </is>
       </c>
       <c r="P449" t="inlineStr">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -37680,7 +37680,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P450" t="inlineStr">
@@ -37777,7 +37777,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P451" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -37874,7 +37874,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P452" t="inlineStr">
@@ -37936,7 +37936,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -37971,7 +37971,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P453" t="inlineStr">
@@ -38028,7 +38028,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>簡単</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -38063,7 +38063,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>簡単に倒せる相手</t>
+          <t>容易打倒的对手</t>
         </is>
       </c>
       <c r="P454" t="inlineStr">
@@ -38155,7 +38155,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P455" t="inlineStr">
@@ -38247,7 +38247,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>そこそこ強いが、余裕で勝利できる</t>
+          <t>相当强，但可以轻松取胜</t>
         </is>
       </c>
       <c r="P456" t="inlineStr">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -38339,7 +38339,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P457" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>強敵</t>
+          <t>强敌</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -38431,7 +38431,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>慎重に相手を選ぼう！</t>
+          <t>仔细选择对手！</t>
         </is>
       </c>
       <c r="P458" t="inlineStr">
@@ -38488,7 +38488,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>戦闘バフ</t>
+          <t>战斗加成</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -38674,7 +38674,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>属性バフ</t>
+          <t>属性增益</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -38860,7 +38860,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -38890,7 +38890,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>何か良いことがあるかもしれない。</t>
+          <t>也许会有什么好事。</t>
         </is>
       </c>
       <c r="P465" t="inlineStr">
@@ -38947,7 +38947,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -38982,7 +38982,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P466" t="inlineStr">
@@ -39049,7 +39049,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>覇者</t>
+          <t>霸主</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -39084,7 +39084,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>強い敵が立ち塞がっている。</t>
+          <t>强大的敌人挡住了去路。</t>
         </is>
       </c>
       <c r="P467" t="inlineStr">
@@ -39141,7 +39141,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>豪華宝箱</t>
+          <t>豪华宝箱</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -39171,7 +39171,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>試練を乗り越えた者に与えられる報酬。</t>
+          <t>给予通过试炼者的报酬。</t>
         </is>
       </c>
       <c r="P468" t="inlineStr">
